--- a/data/trans_bre/P32-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,4</t>
+          <t>-3,0; -0,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -1,54</t>
+          <t>-7,71; -1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,24</t>
+          <t>-3,35; 2,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,88</t>
+          <t>-2,54; 1,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,78; -23,47</t>
+          <t>-93,55; -17,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 107,76</t>
+          <t>-78,82; 141,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,41; 197,66</t>
+          <t>-84,69; 198,86</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,23</t>
+          <t>-3,72; -0,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,71</t>
+          <t>-5,74; -0,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; -0,54</t>
+          <t>-5,61; -0,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,7</t>
+          <t>-4,28; 3,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,5</t>
+          <t>-100,0; 15,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,21; -4,16</t>
+          <t>-91,94; -1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,33; -8,08</t>
+          <t>-80,42; -0,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 87,07</t>
+          <t>-59,15; 97,43</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,34</t>
+          <t>-5,52; 0,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -3,09</t>
+          <t>-9,36; -3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,35</t>
+          <t>-5,29; 0,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -0,0</t>
+          <t>-9,68; -0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,09</t>
+          <t>-100,0; 26,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-94,46; -35,09</t>
+          <t>-93,78; -46,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-86,95; 17,67</t>
+          <t>-83,28; 50,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-96,54; 4,18</t>
+          <t>-96,74; -1,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 3,23</t>
+          <t>-2,22; 2,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,62</t>
+          <t>-7,48; -1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,34</t>
+          <t>-4,76; 1,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -5,32</t>
+          <t>-12,41; -5,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 150,38</t>
+          <t>-62,24; 163,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,16; -23,34</t>
+          <t>-83,34; -17,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,65; 25,82</t>
+          <t>-61,53; 23,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,88; -69,79</t>
+          <t>-94,98; -70,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,07</t>
+          <t>-2,35; -0,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -2,87</t>
+          <t>-6,12; -3,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,61</t>
+          <t>-3,37; -0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,92</t>
+          <t>-5,85; -2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 2,35</t>
+          <t>-73,81; -4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-80,37; -46,23</t>
+          <t>-81,63; -51,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,58; -10,58</t>
+          <t>-57,76; -9,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,51; -35,92</t>
+          <t>-81,43; -38,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-29,57%</t>
+          <t>-30,31%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -0,24</t>
+          <t>-2,83; -0,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -1,68</t>
+          <t>-7,61; -1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,65</t>
+          <t>-3,39; 2,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,79</t>
+          <t>-2,64; 1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,55; -17,21</t>
+          <t>-93,17; -21,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,82; 141,57</t>
+          <t>-82,27; 125,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,69; 198,86</t>
+          <t>-82,9; 130,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,47%</t>
+          <t>-11,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,21</t>
+          <t>-3,82; -0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,67</t>
+          <t>-6,05; -0,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,65</t>
+          <t>-5,79; -0,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,64</t>
+          <t>-4,27; 3,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,4</t>
+          <t>-100,0; 10,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,94; -1,99</t>
+          <t>-91,54; 8,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,42; -0,68</t>
+          <t>-80,49; -5,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 97,43</t>
+          <t>-61,12; 80,69</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,08</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-64,7%</t>
+          <t>-27,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,28</t>
+          <t>-5,56; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -3,24</t>
+          <t>-9,6; -3,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 0,82</t>
+          <t>-5,55; 0,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -0,24</t>
+          <t>-6,5; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,52</t>
+          <t>-100,0; 68,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-93,78; -46,18</t>
+          <t>-94,36; -39,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 50,01</t>
+          <t>-86,23; 39,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-96,74; -1,86</t>
+          <t>-68,52; 74,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,29</t>
+          <t>-7,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-87,07%</t>
+          <t>-80,1%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,87</t>
+          <t>-2,47; 2,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -1,4</t>
+          <t>-7,8; -1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1,26</t>
+          <t>-4,55; 1,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -5,31</t>
+          <t>-11,03; -4,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,24; 163,02</t>
+          <t>-68,33; 159,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,34; -17,45</t>
+          <t>-84,53; -21,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 23,32</t>
+          <t>-56,97; 27,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,98; -70,0</t>
+          <t>-92,97; -45,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-61,46%</t>
+          <t>-46,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,16</t>
+          <t>-2,36; -0,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -3,12</t>
+          <t>-6,2; -3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,4</t>
+          <t>-3,52; -0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -2,04</t>
+          <t>-4,72; -1,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,81; -4,48</t>
+          <t>-71,69; 0,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-81,63; -51,27</t>
+          <t>-81,97; -50,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-57,76; -9,03</t>
+          <t>-57,61; -8,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,43; -38,19</t>
+          <t>-64,6; -15,54</t>
         </is>
       </c>
     </row>
